--- a/files/九龙-启德-Monaco One.xlsx
+++ b/files/九龙-启德-Monaco One.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -23319,155 +23357,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco One - 2A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>246 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>246 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 331呎 (1房)
-$1,015万
+$1015万
 $30,659/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $902万
@@ -23475,23 +23513,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 483呎 (2房)
-$1,470万
+$1470万
 $30,437/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,068万
+$1068万
 $24,065/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $813万
@@ -23499,7 +23537,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $844万
@@ -23508,29 +23546,29 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,900万
+$1900万
 $28,322/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,213万
+$1213万
 $27,814/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $840万
@@ -23538,7 +23576,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $897万
@@ -23546,23 +23584,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,148万
+$1148万
 $25,733/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,092万
+$1092万
 $24,601/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $832万
@@ -23570,7 +23608,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $840万
@@ -23579,29 +23617,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,783万
+$1783万
 $26,577/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,172万
+$1172万
 $26,869/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $837万
@@ -23609,7 +23647,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $894万
@@ -23617,23 +23655,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,178万
+$1178万
 $26,470/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,056万
+$1056万
 $23,726/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $807万
@@ -23641,7 +23679,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $839万
@@ -23650,29 +23688,29 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,828万
+$1828万
 $27,249/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,169万
+$1169万
 $26,814/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $833万
@@ -23680,7 +23718,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $867万
@@ -23688,23 +23726,23 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,143万
+$1143万
 $25,688/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,053万
+$1053万
 $23,707/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $829万
@@ -23712,7 +23750,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $814万
@@ -23721,29 +23759,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,773万
+$1773万
 $26,417/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,134万
+$1134万
 $26,021/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $854万
@@ -23751,7 +23789,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $864万
@@ -23759,23 +23797,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,141万
+$1141万
 $25,636/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,050万
+$1050万
 $23,584/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $827万
@@ -23783,7 +23821,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $835万
@@ -23792,29 +23830,29 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,818万
+$1818万
 $27,088/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,132万
+$1132万
 $25,970/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $828万
@@ -23822,7 +23860,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $901万
@@ -23830,23 +23868,23 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,138万
+$1138万
 $25,527/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,050万
+$1050万
 $23,584/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $825万
@@ -23854,7 +23892,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $834万
@@ -23863,29 +23901,29 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,812万
+$1812万
 $27,006/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,162万
+$1162万
 $26,656/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $827万
@@ -23893,7 +23931,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $883万
@@ -23901,23 +23939,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,136万
+$1136万
 $25,475/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,046万
+$1046万
 $23,515/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $801万
@@ -23925,7 +23963,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $832万
@@ -23934,29 +23972,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,807万
+$1807万
 $26,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,158万
+$1158万
 $26,548/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $848万
@@ -23964,7 +24002,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $881万
@@ -23972,23 +24010,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,166万
+$1166万
 $26,148/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,073万
+$1073万
 $24,108/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $799万
@@ -23996,7 +24034,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $830万
@@ -24005,29 +24043,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,752万
+$1752万
 $26,103/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,123万
+$1123万
 $25,764/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $822万
@@ -24035,7 +24073,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $868万
@@ -24043,23 +24081,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,132万
+$1132万
 $25,431/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,072万
+$1072万
 $24,099/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $820万
@@ -24067,7 +24105,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $819万
@@ -24076,29 +24114,29 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,733万
+$1733万
 $25,832/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,153万
+$1153万
 $26,443/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $820万
@@ -24106,7 +24144,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $866万
@@ -24114,23 +24152,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,129万
+$1129万
 $25,323/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,052万
+$1052万
 $23,682/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $819万
@@ -24138,7 +24176,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $827万
@@ -24147,29 +24185,29 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,723万
+$1723万
 $25,678/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,115万
+$1115万
 $25,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $836万
@@ -24177,7 +24215,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $870万
@@ -24185,23 +24223,23 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,122万
+$1122万
 $25,168/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,057万
+$1057万
 $23,804/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $812万
@@ -24209,7 +24247,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $802万
@@ -24218,29 +24256,29 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,718万
+$1718万
 $25,601/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,113万
+$1113万
 $25,521/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $824万
@@ -24248,7 +24286,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $868万
@@ -24256,23 +24294,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,120万
+$1120万
 $25,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,042万
+$1042万
 $23,471/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $810万
@@ -24280,7 +24318,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $812万
@@ -24289,29 +24327,29 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,756万
+$1756万
 $26,171/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,144万
+$1144万
 $26,234/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $831万
@@ -24319,7 +24357,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $865万
@@ -24327,23 +24365,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,136万
+$1136万
 $25,528/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,022万
+$1022万
 $22,957/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $786万
@@ -24351,7 +24389,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $819万
@@ -24360,29 +24398,29 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,702万
+$1702万
 $25,373/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,109万
+$1109万
 $25,445/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $829万
@@ -24390,7 +24428,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $862万
@@ -24398,23 +24436,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,114万
+$1114万
 $24,980/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,048万
+$1048万
 $23,539/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $784万
@@ -24422,7 +24460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $814万
@@ -24431,29 +24469,29 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,746万
+$1746万
 $26,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,138万
+$1138万
 $26,103/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $828万
@@ -24461,7 +24499,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $860万
@@ -24469,23 +24507,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,130万
+$1130万
 $25,343/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,044万
+$1044万
 $23,467/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $804万
@@ -24493,7 +24531,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $812万
@@ -24502,29 +24540,29 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,692万
+$1692万
 $25,221/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,133万
+$1133万
 $25,984/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $826万
@@ -24532,7 +24570,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $834万
@@ -24540,23 +24578,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,109万
+$1109万
 $24,912/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,012万
+$1012万
 $22,753/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $802万
@@ -24564,7 +24602,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $788万
@@ -24573,29 +24611,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,687万
+$1687万
 $25,146/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,099万
+$1099万
 $25,204/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $798万
@@ -24603,7 +24641,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $831万
@@ -24611,23 +24649,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,106万
+$1106万
 $24,849/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,038万
+$1038万
 $23,381/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $800万
@@ -24635,7 +24673,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $808万
@@ -24644,29 +24682,29 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,687万
+$1687万
 $25,146/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,127万
+$1127万
 $25,856/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $818万
@@ -24674,7 +24712,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $829万
@@ -24682,23 +24720,23 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,134万
+$1134万
 $25,492/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,035万
+$1035万
 $23,311/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $798万
@@ -24706,7 +24744,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $806万
@@ -24715,29 +24753,29 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,682万
+$1682万
 $25,070/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,124万
+$1124万
 $25,791/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $816万
@@ -24745,7 +24783,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $826万
@@ -24753,23 +24791,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,100万
+$1100万
 $24,670/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,003万
+$1003万
 $22,548/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $796万
@@ -24777,7 +24815,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $804万
@@ -24786,29 +24824,29 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,672万
+$1672万
 $24,920/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,108万
+$1108万
 $25,417/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $811万
@@ -24816,7 +24854,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $821万
@@ -24824,15 +24862,15 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,125万
+$1125万
 $25,231/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
 $997万
@@ -24840,7 +24878,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $792万
@@ -24848,7 +24886,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $800万
@@ -24857,29 +24895,29 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,698万
+$1698万
 $25,300/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,076万
+$1076万
 $24,683/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $786万
@@ -24887,7 +24925,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $842万
@@ -24895,15 +24933,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,122万
+$1122万
 $25,168/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
 $994万
@@ -24911,7 +24949,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $790万
@@ -24919,7 +24957,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $798万
@@ -24928,29 +24966,29 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,668万
+$1668万
 $24,852/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,058万
+$1058万
 $24,257/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $784万
@@ -24958,7 +24996,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $839万
@@ -24966,15 +25004,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,088万
+$1088万
 $24,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
 $992万
@@ -24982,7 +25020,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $788万
@@ -24990,7 +25028,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $796万
@@ -24999,29 +25037,29 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,644万
+$1644万
 $24,505/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,084万
+$1084万
 $24,872/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $804万
@@ -25029,7 +25067,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $814万
@@ -25037,15 +25075,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,084万
+$1084万
 $24,312/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
 $988万
@@ -25053,7 +25091,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $787万
@@ -25061,7 +25099,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $793万
@@ -25070,29 +25108,29 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,706万
+$1706万
 $25,422/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,081万
+$1081万
 $24,800/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $779万
@@ -25100,7 +25138,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $834万
@@ -25108,15 +25146,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,081万
+$1081万
 $24,292/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
 $986万
@@ -25124,7 +25162,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $786万
@@ -25132,7 +25170,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $769万
@@ -25141,29 +25179,29 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,646万
+$1646万
 $24,532/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,048万
+$1048万
 $24,041/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $790万
@@ -25171,7 +25209,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $832万
@@ -25179,15 +25217,15 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,108万
+$1108万
 $24,908/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
 $983万
@@ -25195,7 +25233,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $786万
@@ -25203,7 +25241,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $789万
@@ -25212,29 +25250,29 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,660万
+$1660万
 $24,739/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,045万
+$1045万
 $23,968/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $796万
@@ -25242,7 +25280,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $830万
@@ -25250,15 +25288,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,105万
+$1105万
 $24,834/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
 $980万
@@ -25266,7 +25304,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $785万
@@ -25274,7 +25312,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $788万
@@ -25283,29 +25321,29 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,655万
+$1655万
 $24,666/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,040万
+$1040万
 $23,851/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $795万
@@ -25313,7 +25351,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $827万
@@ -25321,23 +25359,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,102万
+$1102万
 $24,704/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,012万
+$1012万
 $22,791/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $784万
@@ -25345,7 +25383,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $765万
@@ -25354,29 +25392,29 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,588万
+$1588万
 $23,665/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,026万
+$1026万
 $23,532/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $790万
@@ -25384,7 +25422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $822万
@@ -25392,23 +25430,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,095万
+$1095万
 $24,556/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,011万
+$1011万
 $22,761/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $781万
@@ -25416,7 +25454,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $784万
@@ -25425,29 +25463,29 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,554万
+$1554万
 $23,152/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,043万
+$1043万
 $23,927/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $788万
@@ -25455,7 +25493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $820万
@@ -25463,23 +25501,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,062万
+$1062万
 $23,861/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,009万
+$1009万
 $22,732/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $780万
@@ -25487,7 +25525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $783万
@@ -25496,29 +25534,29 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,549万
+$1549万
 $23,083/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,011万
+$1011万
 $23,195/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $785万
@@ -25526,7 +25564,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $817万
@@ -25534,23 +25572,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 446呎 (2房)
-$1,095万
+$1095万
 $24,545/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 444呎 (2房)
-$1,006万
+$1006万
 $22,662/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $779万
@@ -25558,7 +25596,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $782万
@@ -25567,29 +25605,29 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 671呎 (3房)
-$1,544万
+$1544万
 $23,016/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
-$1,008万
+$1008万
 $23,126/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 326呎 (1房)
 $761万
@@ -25597,7 +25635,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 326呎 (1房)
 $815万
@@ -25605,23 +25643,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,055万
+$1055万
 $23,717/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 445呎 (2房)
-$1,001万
+$1001万
 $22,499/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $778万
@@ -25629,7 +25667,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 321呎 (1房)
 $782万
@@ -25640,7 +25678,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -25653,163 +25691,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco One - 2B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>246 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>245 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1471呎 (4+房)
-$5,275万
+$5275万
 $35,860/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1,141万
+$1141万
 $25,927/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $906万
@@ -25817,15 +25855,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
-$1,001万
+$1001万
 $30,432/呎
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $840万
@@ -25833,7 +25871,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $847万
@@ -25842,45 +25880,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,391万
+$1391万
 $25,380/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,454万
+$1454万
 $27,845/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,274万
+$1274万
 $25,902/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,166万
+$1166万
 $25,123/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $876万
@@ -25888,7 +25926,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $876万
@@ -25896,7 +25934,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $858万
@@ -25904,7 +25942,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $842万
@@ -25913,45 +25951,45 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,387万
+$1387万
 $25,305/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,497万
+$1497万
 $28,682/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,292万
+$1292万
 $26,266/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,186万
+$1186万
 $25,552/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $898万
@@ -25959,7 +25997,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $898万
@@ -25967,7 +26005,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $856万
@@ -25975,7 +26013,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $816万
@@ -25984,45 +26022,45 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,382万
+$1382万
 $25,228/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,405万
+$1405万
 $26,914/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,303万
+$1303万
 $26,480/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,163万
+$1163万
 $25,071/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $895万
@@ -26030,7 +26068,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $871万
@@ -26038,7 +26076,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $853万
@@ -26046,7 +26084,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $814万
@@ -26055,45 +26093,45 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,418万
+$1418万
 $25,869/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,401万
+$1401万
 $26,833/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,263万
+$1263万
 $25,671/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,192万
+$1192万
 $25,683/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $868万
@@ -26101,7 +26139,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $868万
@@ -26109,7 +26147,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $827万
@@ -26117,7 +26155,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $834万
@@ -26126,45 +26164,45 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,374万
+$1374万
 $25,078/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,396万
+$1396万
 $26,753/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,259万
+$1259万
 $25,593/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,156万
+$1156万
 $24,922/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $865万
@@ -26172,7 +26210,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $865万
@@ -26180,7 +26218,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $848万
@@ -26188,7 +26226,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $807万
@@ -26197,45 +26235,45 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,409万
+$1409万
 $25,712/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,432万
+$1432万
 $27,431/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,256万
+$1256万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,156万
+$1156万
 $24,922/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $887万
@@ -26243,7 +26281,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $887万
@@ -26251,7 +26289,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $822万
@@ -26259,7 +26297,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $828万
@@ -26268,45 +26306,45 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,366万
+$1366万
 $24,929/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,388万
+$1388万
 $26,594/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,252万
+$1252万
 $25,441/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,154万
+$1154万
 $24,873/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $860万
@@ -26314,7 +26352,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $885万
@@ -26322,7 +26360,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $843万
@@ -26330,7 +26368,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $827万
@@ -26339,45 +26377,45 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,362万
+$1362万
 $24,852/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,384万
+$1384万
 $26,513/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,248万
+$1248万
 $25,366/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,150万
+$1150万
 $24,774/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $882万
@@ -26385,7 +26423,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $882万
@@ -26393,7 +26431,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $840万
@@ -26401,7 +26439,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $824万
@@ -26410,45 +26448,45 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,358万
+$1358万
 $24,779/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,604万
+$1604万
 $30,726/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,263万
+$1263万
 $25,669/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,147万
+$1147万
 $24,724/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $879万
@@ -26456,7 +26494,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $879万
@@ -26464,7 +26502,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $829万
@@ -26472,7 +26510,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $822万
@@ -26481,45 +26519,45 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,388万
+$1388万
 $25,330/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,372万
+$1372万
 $26,276/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,255万
+$1255万
 $25,516/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,176万
+$1176万
 $25,351/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $876万
@@ -26527,7 +26565,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $876万
@@ -26535,7 +26573,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $833万
@@ -26543,7 +26581,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $815万
@@ -26552,45 +26590,45 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,384万
+$1384万
 $25,255/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,315万
+$1315万
 $25,192/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,231万
+$1231万
 $25,012/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,173万
+$1173万
 $25,289/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $874万
@@ -26598,7 +26636,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $850万
@@ -26606,7 +26644,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $806万
@@ -26614,7 +26652,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $813万
@@ -26623,45 +26661,45 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,342万
+$1342万
 $24,484/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,348万
+$1348万
 $25,830/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,227万
+$1227万
 $24,937/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,138万
+$1138万
 $24,528/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $871万
@@ -26669,7 +26707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $871万
@@ -26677,7 +26715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $826万
@@ -26685,7 +26723,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $788万
@@ -26694,45 +26732,45 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,421万
+$1421万
 $25,936/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,307万
+$1307万
 $25,042/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,258万
+$1258万
 $25,571/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,135万
+$1135万
 $24,466/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $844万
@@ -26740,7 +26778,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $868万
@@ -26748,7 +26786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $826万
@@ -26756,7 +26794,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $810万
@@ -26765,45 +26803,45 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,334万
+$1334万
 $24,338/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,303万
+$1303万
 $24,966/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,222万
+$1222万
 $24,839/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,162万
+$1162万
 $25,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $866万
@@ -26811,7 +26849,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $866万
@@ -26819,7 +26857,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $800万
@@ -26827,7 +26865,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $807万
@@ -26836,45 +26874,45 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,368万
+$1368万
 $24,954/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,322万
+$1322万
 $25,316/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,218万
+$1218万
 $24,764/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,127万
+$1127万
 $24,295/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $863万
@@ -26882,7 +26920,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $863万
@@ -26890,7 +26928,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $798万
@@ -26898,7 +26936,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $805万
@@ -26907,45 +26945,45 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,326万
+$1326万
 $24,193/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,318万
+$1318万
 $25,241/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,249万
+$1249万
 $25,392/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,124万
+$1124万
 $24,235/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $837万
@@ -26953,7 +26991,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $861万
@@ -26961,7 +26999,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $816万
@@ -26969,7 +27007,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $780万
@@ -26978,45 +27016,45 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,359万
+$1359万
 $24,807/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,292万
+$1292万
 $24,743/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,211万
+$1211万
 $24,616/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,179万
+$1179万
 $25,412/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $834万
@@ -27024,7 +27062,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $858万
@@ -27032,7 +27070,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $814万
@@ -27040,7 +27078,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $800万
@@ -27049,45 +27087,45 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,355万
+$1355万
 $24,732/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,324万
+$1324万
 $25,370/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,205万
+$1205万
 $24,494/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,153万
+$1153万
 $24,849/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $846万
@@ -27095,7 +27133,7 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $856万
@@ -27103,7 +27141,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $813万
@@ -27111,7 +27149,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $776万
@@ -27120,45 +27158,45 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,310万
+$1310万
 $23,905/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,280万
+$1280万
 $24,523/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,198万
+$1198万
 $24,348/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,147万
+$1147万
 $24,713/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $829万
@@ -27166,7 +27204,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $850万
@@ -27174,7 +27212,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $786万
@@ -27182,7 +27220,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $791万
@@ -27191,45 +27229,45 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,330万
+$1330万
 $24,268/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,264万
+$1264万
 $24,207/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,194万
+$1194万
 $24,276/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,112万
+$1112万
 $23,972/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $848万
@@ -27237,7 +27275,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $848万
@@ -27245,7 +27283,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $784万
@@ -27253,7 +27291,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $789万
@@ -27262,45 +27300,45 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,269万
+$1269万
 $23,157/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,277万
+$1277万
 $24,456/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,179万
+$1179万
 $23,963/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,110万
+$1110万
 $23,912/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $847万
@@ -27308,7 +27346,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $847万
@@ -27316,7 +27354,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $802万
@@ -27324,7 +27362,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $788万
@@ -27333,45 +27371,45 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,301万
+$1301万
 $23,745/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,238万
+$1238万
 $23,709/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,176万
+$1176万
 $23,892/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,104万
+$1104万
 $23,791/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $859万
@@ -27379,7 +27417,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $845万
@@ -27387,7 +27425,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $800万
@@ -27395,7 +27433,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $787万
@@ -27404,45 +27442,45 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,261万
+$1261万
 $23,018/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,269万
+$1269万
 $24,310/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,269万
+$1269万
 $25,787/呎
 (22年-12月)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,132万
+$1132万
 $24,394/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $842万
@@ -27450,7 +27488,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $819万
@@ -27458,7 +27496,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $797万
@@ -27466,7 +27504,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $787万
@@ -27475,45 +27513,45 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,279万
+$1279万
 $23,341/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,265万
+$1265万
 $24,236/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,202万
+$1202万
 $24,425/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,100万
+$1100万
 $23,696/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $817万
@@ -27521,7 +27559,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $840万
@@ -27529,7 +27567,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $795万
@@ -27537,7 +27575,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $764万
@@ -27546,45 +27584,45 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,290万
+$1290万
 $23,533/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,226万
+$1226万
 $23,496/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,167万
+$1167万
 $23,726/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,096万
+$1096万
 $23,627/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 328呎 (1房)
 $837万
@@ -27592,7 +27630,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $794万
@@ -27600,7 +27638,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $792万
@@ -27608,7 +27646,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $784万
@@ -27617,45 +27655,45 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,250万
+$1250万
 $22,814/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,258万
+$1258万
 $24,090/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,164万
+$1164万
 $23,654/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,088万
+$1088万
 $23,450/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $835万
@@ -27663,7 +27701,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $835万
@@ -27671,7 +27709,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $790万
@@ -27679,7 +27717,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $783万
@@ -27688,45 +27726,45 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,269万
+$1269万
 $23,150/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,206万
+$1206万
 $23,113/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,155万
+$1155万
 $23,467/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,082万
+$1082万
 $23,310/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $821万
@@ -27734,7 +27772,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $830万
@@ -27742,7 +27780,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $765万
@@ -27750,7 +27788,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $781万
@@ -27759,45 +27797,45 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,255万
+$1255万
 $22,909/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,228万
+$1228万
 $23,525/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,178万
+$1178万
 $23,941/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,078万
+$1078万
 $23,239/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $827万
@@ -27805,7 +27843,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $827万
@@ -27813,7 +27851,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $786万
@@ -27821,7 +27859,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 319呎 (1房)
 $780万
@@ -27830,45 +27868,45 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,252万
+$1252万
 $22,841/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,224万
+$1224万
 $23,452/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 492呎 (2房)
-$1,142万
+$1142万
 $23,211/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,106万
+$1106万
 $23,830/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $825万
@@ -27876,7 +27914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 328呎 (1房)
 $825万
@@ -27884,7 +27922,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $785万
@@ -27892,7 +27930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $758万
@@ -27901,45 +27939,45 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 548呎 (3房)
-$1,248万
+$1248万
 $22,772/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 522呎 (3房)
-$1,187万
+$1187万
 $22,738/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 476呎 (2房)
-$1,168万
+$1168万
 $24,538/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 464呎 (2房)
-$1,102万
+$1102万
 $23,756/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 329呎 (1房)
 $822万
@@ -27947,7 +27985,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 329呎 (1房)
 $822万
@@ -27955,7 +27993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $785万
@@ -27963,7 +28001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 320呎 (1房)
 $779万
@@ -27974,7 +28012,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
